--- a/results/log_pv_cap_per_inst_fit/log_pv_cap_per_inst_fit_densities_fdensity_estimates.xlsx
+++ b/results/log_pv_cap_per_inst_fit/log_pv_cap_per_inst_fit_densities_fdensity_estimates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,41 +462,11 @@
           <t>densities-ML_ErrorFE-queen-Running ML_ErrorFE:queen for log_pv_cap_per_inst_fit ~ (densities): fdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>densities-PooledOLS-inverse_distance-Running PooledOLS:inverse_distance for log_pv_cap_per_inst_fit ~ (densities): fdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>densities-PooledOLS-k_nearest-Running PooledOLS:k_nearest for log_pv_cap_per_inst_fit ~ (densities): fdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>densities-PooledOLS-queen-Running PooledOLS:queen for log_pv_cap_per_inst_fit ~ (densities): fdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>densities-PanelRE-inverse_distance-Running PanelRE:inverse_distance for log_pv_cap_per_inst_fit ~ (densities): fdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>densities-PanelRE-k_nearest-Running PanelRE:k_nearest for log_pv_cap_per_inst_fit ~ (densities): fdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>densities-PanelRE-queen-Running PanelRE:queen for log_pv_cap_per_inst_fit ~ (densities): fdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>fdensity</t>
+          <t>D(Firms)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -540,36 +510,6 @@
         </is>
       </c>
       <c r="J2" t="inlineStr">
-        <is>
-          <t>0.003***</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0.003***</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0.003***</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
         <is>
           <t>0.003***</t>
         </is>
@@ -578,7 +518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>log_income</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -624,43 +564,13 @@
       <c r="J3" t="inlineStr">
         <is>
           <t>0.138***</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.071***</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0.071***</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0.071***</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0.130***</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0.130***</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0.130***</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>log_hholds</t>
+          <t>Households</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -704,36 +614,6 @@
         </is>
       </c>
       <c r="J4" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-0.003**</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-0.003**</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>-0.003**</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
         <is>
           <t>-0.000</t>
         </is>
@@ -742,7 +622,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>log_sunny_hours</t>
+          <t>Sunny hours</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -788,126 +668,96 @@
       <c r="J5" t="inlineStr">
         <is>
           <t>-0.046***</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-0.109***</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-0.109***</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>-0.109***</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>-0.051***</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>-0.051***</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>-0.051***</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W_fdensity</t>
+          <t>Spatial term, ρ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.017*</t>
+          <t>0.598***</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.002+</t>
+          <t>0.198***</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>0.116***</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.610***</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.224***</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.128***</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W_log_income</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>0.042</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0.040+</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.033</t>
-        </is>
-      </c>
+          <t>Spatial term, λ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.719***</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.209***</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.119***</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W_log_hholds</t>
+          <t>W(D(Firms))</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>-0.017*</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>-0.002+</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -916,32 +766,26 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>W_log_sunny_hours</t>
+          <t>W(Income)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>0.042</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.013</t>
+          <t>0.040+</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-0.030*</t>
+          <t>0.033</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -950,891 +794,320 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>W_log_pv_cap_per_inst_fit</t>
+          <t>W(Households)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.598***</t>
+          <t>-0.001</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.198***</t>
+          <t>0.001</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.116***</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.610***</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0.224***</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0.128***</t>
-        </is>
-      </c>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>r2</t>
+          <t>W(Sunny hours)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>0.012</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.230</t>
+          <t>-0.013</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.229</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.241</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0.229</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0.226</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.213</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.214</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.214</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.042</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0.042</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0.042</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.025</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.025</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0.025</t>
-        </is>
-      </c>
+          <t>-0.030*</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>aic</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-14808.429</t>
+          <t>0.245</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-14767.097</t>
+          <t>0.230</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-14766.153</t>
+          <t>0.229</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-14806.291</t>
+          <t>0.241</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-14768.731</t>
+          <t>0.229</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-14765.353</t>
+          <t>0.226</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-14809.679</t>
+          <t>0.213</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-14764.466</t>
+          <t>0.214</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-14761.462</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>-7626.488</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-7626.488</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>-7626.488</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>-7475.142</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>-7475.142</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>-7475.142</t>
+          <t>0.214</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>schwarz</t>
+          <t>AIC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-14757.685</t>
+          <t>-14808.429</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-14716.353</t>
+          <t>-14767.097</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-14715.409</t>
+          <t>-14766.153</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-14778.100</t>
+          <t>-14806.291</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-14740.540</t>
+          <t>-14768.731</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-14737.162</t>
+          <t>-14765.353</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-14787.126</t>
+          <t>-14809.679</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-14741.913</t>
+          <t>-14764.466</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-14738.909</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>-7598.297</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>-7598.297</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>-7598.297</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>-7446.951</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>-7446.951</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>-7446.951</t>
+          <t>-14761.462</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>llr</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7413.215</t>
+          <t>-14757.685</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>7392.549</t>
+          <t>-14716.353</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7392.077</t>
+          <t>-14715.409</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>7408.146</t>
+          <t>-14778.100</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>7389.365</t>
+          <t>-14740.540</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>7387.677</t>
+          <t>-14737.162</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7408.839</t>
+          <t>-14787.126</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>7386.233</t>
+          <t>-14741.913</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>7384.731</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>3818.244</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>3818.244</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>3818.244</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>3742.571</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>3742.571</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>3742.571</t>
+          <t>-14738.909</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>n_obs</t>
+          <t>Log-Likelihood</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>7413.215</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>7392.549</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>7392.077</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>7408.146</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>7389.365</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>7387.677</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>7408.839</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>7386.233</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2076</t>
+          <t>7384.731</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tests</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df   p-value
-0       LM Marginal RE (LM1)    68.673268   1  0.000000
-1  LM Marginal Spatial (LM2)     0.196059   1  0.422282
-2             LM Joint (LMJ)  4716.056122   2  0.000000</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df   p-value
-0       LM Marginal RE (LM1)    68.673268   1  0.000000
-1  LM Marginal Spatial (LM2)    -1.840124   1  0.967125
-2             LM Joint (LMJ)  4716.017683   2  0.000000</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df   p-value
-0       LM Marginal RE (LM1)    68.673268   1  0.000000
-1  LM Marginal Spatial (LM2)    -2.831451   1  0.997683
-2             LM Joint (LMJ)  4716.017683   2  0.000000</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test  Statistic df p-value
-0      LM Conditional Spatial  15.186118  1     0.0
-1  Hausman Specification Test  41.401288  4     0.0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test  Statistic df   p-value
-0      LM Conditional Spatial   4.541562  1  0.000003
-1  Hausman Specification Test  41.401288  4       0.0</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test  Statistic df p-value
-0      LM Conditional Spatial   5.114644  1     0.0
-1  Hausman Specification Test  41.401288  4     0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>outputs</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                   var_names coefficients   std_err   zt_stat      prob
-0                   fdensity     0.003566  0.000426  8.365724       0.0
-1                 log_income     0.095132  0.022109  4.302853  0.000017
-2                 log_hholds    -0.000053  0.000359  -0.14681  0.883282
-3            log_sunny_hours    -0.038828  0.010365 -3.745978   0.00018
-4                 W_fdensity    -0.016728  0.008378 -1.996624  0.045866
-5               W_log_income     0.041675   0.04767  0.874231  0.381993
-6               W_log_hholds    -0.001158  0.004631 -0.249992  0.802594
-7          W_log_sunny_hours     0.012083  0.015861  0.761823  0.446166
-8  W_log_pv_cap_per_inst_fit     0.598122  0.096613  6.190883       0.0</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                   var_names coefficients   std_err   zt_stat      prob
-0                   fdensity     0.003387  0.000434  7.801937       0.0
-1                 log_income     0.089565  0.021186  4.227599  0.000024
-2                 log_hholds    -0.000116  0.000364 -0.318434  0.750156
-3            log_sunny_hours    -0.038608  0.009898 -3.900443  0.000096
-4                 W_fdensity    -0.002312  0.001206 -1.916926  0.055247
-5               W_log_income      0.04002  0.024165  1.656115  0.097699
-6               W_log_hholds     0.000531  0.001081   0.49133  0.623193
-7          W_log_sunny_hours    -0.012717  0.012967 -0.980675  0.326753
-8  W_log_pv_cap_per_inst_fit     0.197802  0.041345  4.784146  0.000002</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                   var_names coefficients   std_err   zt_stat      prob
-0                   fdensity     0.003379  0.000433  7.800916       0.0
-1                 log_income     0.099254  0.020179  4.918641  0.000001
-2                 log_hholds    -0.000215  0.000363 -0.593536  0.552823
-3            log_sunny_hours    -0.030768   0.00967 -3.181658  0.001464
-4                 W_fdensity    -0.000473  0.000916 -0.516667  0.605389
-5               W_log_income     0.032868  0.021565  1.524133  0.127475
-6               W_log_hholds     0.000082  0.000592   0.13853  0.889821
-7          W_log_sunny_hours    -0.030038  0.012038 -2.495328  0.012584
-8  W_log_pv_cap_per_inst_fit     0.116199  0.032154  3.613824  0.000302</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                   var_names coefficients   std_err   zt_stat      prob
-0                   fdensity     0.003487  0.000425  8.200135       0.0
-1                 log_income      0.05978  0.013187  4.533349  0.000006
-2                 log_hholds     -0.00016  0.000358 -0.447646  0.654408
-3            log_sunny_hours    -0.034199  0.007461 -4.583814  0.000005
-4  W_log_pv_cap_per_inst_fit     0.609739  0.068569  8.892308       0.0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                   var_names coefficients   std_err    zt_stat      prob
-0                   fdensity     0.003395  0.000429   7.919184       0.0
-1                 log_income     0.111666  0.009008  12.396675       0.0
-2                 log_hholds    -0.000208  0.000361  -0.575678  0.564833
-3            log_sunny_hours    -0.043965  0.007107  -6.185833       0.0
-4  W_log_pv_cap_per_inst_fit     0.223741  0.038216   5.854663       0.0</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                   var_names coefficients   std_err    zt_stat      prob
-0                   fdensity     0.003383   0.00043   7.876405       0.0
-1                 log_income     0.122193  0.008485  14.400969       0.0
-2                 log_hholds    -0.000222  0.000361  -0.613248  0.539712
-3            log_sunny_hours    -0.045666  0.007096  -6.435411       0.0
-4  W_log_pv_cap_per_inst_fit     0.128143  0.030712   4.172434   0.00003</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err   zt_stat      prob
-0         fdensity     0.003627  0.000425  8.532305       0.0
-1       log_income     0.122717  0.016568  7.407084       0.0
-2       log_hholds    -0.000082  0.000357 -0.229118  0.818778
-3  log_sunny_hours    -0.038904  0.009827 -3.958972  0.000075
-4           lambda     0.719357  0.073187  9.829044       0.0</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         fdensity     0.003493   0.00043   8.120688       0.0
-1       log_income     0.138773  0.008798  15.772948       0.0
-2       log_hholds    -0.000174   0.00036   -0.48389  0.628464
-3  log_sunny_hours    -0.046175  0.007878  -5.861477       0.0
-4           lambda     0.208712  0.041056   5.083619       0.0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         fdensity      0.00344  0.000432   7.963722       0.0
-1       log_income     0.138457  0.008135  17.020895       0.0
-2       log_hholds    -0.000208   0.00036  -0.576051  0.564581
-3  log_sunny_hours    -0.046436  0.007537  -6.160858       0.0
-4           lambda     0.118549   0.03215   3.687377  0.000227</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     0.704328   0.06091  11.563454       0.0
-1         fdensity     0.000159  0.000594     0.2676  0.789034
-2       log_income       0.0714  0.009699   7.361665       0.0
-3       log_hholds    -0.002865  0.001026  -2.791408  0.005296
-4  log_sunny_hours    -0.109255  0.018439  -5.925139       0.0</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     0.704328   0.06091  11.563454       0.0
-1         fdensity     0.000159  0.000594     0.2676  0.789034
-2       log_income       0.0714  0.009699   7.361665       0.0
-3       log_hholds    -0.002865  0.001026  -2.791408  0.005296
-4  log_sunny_hours    -0.109255  0.018439  -5.925139       0.0</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     0.704328   0.06091  11.563454       0.0
-1         fdensity     0.000159  0.000594     0.2676  0.789034
-2       log_income       0.0714  0.009699   7.361665       0.0
-3       log_hholds    -0.002865  0.001026  -2.791408  0.005296
-4  log_sunny_hours    -0.109255  0.018439  -5.925139       0.0</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     0.251044  0.036662   6.847447       0.0
-1         fdensity     0.003001  0.000454   6.616265       0.0
-2       log_income     0.130424  0.007712  16.910992       0.0
-3       log_hholds    -0.000196  0.000397  -0.492445  0.622405
-4  log_sunny_hours    -0.050975  0.007755  -6.572994       0.0</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     0.251044  0.036662   6.847447       0.0
-1         fdensity     0.003001  0.000454   6.616265       0.0
-2       log_income     0.130424  0.007712  16.910992       0.0
-3       log_hholds    -0.000196  0.000397  -0.492445  0.622405
-4  log_sunny_hours    -0.050975  0.007755  -6.572994       0.0</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     0.251044  0.036662   6.847447       0.0
-1         fdensity     0.003001  0.000454   6.616265       0.0
-2       log_income     0.130424  0.007712  16.910992       0.0
-3       log_hholds    -0.000196  0.000397  -0.492445  0.622405
-4  log_sunny_hours    -0.050975  0.007755  -6.572994       0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>effects</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_inverse_distance  \
-fdensity                                    -0.032752   
-log_income                                   0.340419   
-log_hholds                                  -0.003012   
-log_sunny_hours                             -0.066550   
-                 direct_ML_LagFE(SLX)_inverse_distance  \
-fdensity                                      0.003566   
-log_income                                    0.095132   
-log_hholds                                   -0.000053   
-log_sunny_hours                              -0.038828   
-                 indirect_ML_LagFE(SLX)_inverse_distance  
-fdensity                                       -0.036318  
-log_income                                      0.245287  
-log_hholds                                     -0.002959  
-log_sunny_hours                                -0.027722  </t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_k_nearest  \
-fdensity                              0.001340   
-log_income                            0.161538   
-log_hholds                            0.000518   
-log_sunny_hours                      -0.063980   
-                 direct_ML_LagFE(SLX)_k_nearest  \
-fdensity                               0.003387   
-log_income                             0.089565   
-log_hholds                            -0.000116   
-log_sunny_hours                       -0.038608   
-                 indirect_ML_LagFE(SLX)_k_nearest  
-fdensity                                -0.002047  
-log_income                               0.071973  
-log_hholds                               0.000634  
-log_sunny_hours                         -0.025372  </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_queen  direct_ML_LagFE(SLX)_queen  \
-fdensity                          0.003288                    0.003379   
-log_income                        0.149494                    0.099254   
-log_hholds                       -0.000151                   -0.000215   
-log_sunny_hours                  -0.068801                   -0.030768   
-                 indirect_ML_LagFE(SLX)_queen  
-fdensity                            -0.000091  
-log_income                           0.050239  
-log_hholds                           0.000065  
-log_sunny_hours                     -0.038033  </t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_inverse_distance  \
-fdensity                                0.008934   
-log_income                              0.153179   
-log_hholds                             -0.000410   
-log_sunny_hours                        -0.087632   
-                 direct_ML_LagFE_inverse_distance  \
-fdensity                                 0.003487   
-log_income                               0.059780   
-log_hholds                              -0.000160   
-log_sunny_hours                         -0.034199   
-                 indirect_ML_LagFE_inverse_distance  
-fdensity                                   0.005447  
-log_income                                 0.093399  
-log_hholds                                -0.000250  
-log_sunny_hours                           -0.053433  </t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_k_nearest  direct_ML_LagFE_k_nearest  \
-fdensity                         0.004374                   0.003395   
-log_income                       0.143852                   0.111666   
-log_hholds                      -0.000267                  -0.000208   
-log_sunny_hours                 -0.056637                  -0.043965   
-                 indirect_ML_LagFE_k_nearest  
-fdensity                            0.000979  
-log_income                          0.032186  
-log_hholds                         -0.000060  
-log_sunny_hours                    -0.012672  </t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_queen  direct_ML_LagFE_queen  \
-fdensity                     0.003881               0.003383   
-log_income                   0.140152               0.122193   
-log_hholds                  -0.000254              -0.000222   
-log_sunny_hours             -0.052377              -0.045666   
-                 indirect_ML_LagFE_queen  
-fdensity                        0.000497  
-log_income                      0.017960  
-log_hholds                     -0.000033  
-log_sunny_hours                -0.006712  </t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>lambda</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>0.719***</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>0.209***</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>0.119***</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>CONSTANT</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>0.704***</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>0.704***</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>0.704***</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>0.251***</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>0.251***</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>0.251***</t>
+          <t>N obs.</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2076</t>
         </is>
       </c>
     </row>
